--- a/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dependencia de mayores</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
@@ -1332,21 +1332,21 @@
         <v>2023</v>
       </c>
       <c r="B22">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I22">
-        <v>35.79242671109532</v>
+        <v>57.84601691143747</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         <v>2023</v>
       </c>
       <c r="B23">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="I23">
-        <v>34.9469918333708</v>
+        <v>57.21308696389219</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1424,21 +1424,21 @@
         <v>2023</v>
       </c>
       <c r="B24">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="I24">
-        <v>34.23672566371682</v>
+        <v>55.6792367105861</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="I25">
-        <v>34.18774966711052</v>
+        <v>53.72091110928378</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         <v>2023</v>
       </c>
       <c r="B26">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="I26">
-        <v>33.90350877192982</v>
+        <v>52.7294438758103</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1562,21 +1562,21 @@
         <v>2023</v>
       </c>
       <c r="B27">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I27">
-        <v>33.80997177798683</v>
+        <v>51.52048253329983</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         <v>2023</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="I28">
-        <v>33.62871067789101</v>
+        <v>51.49797570850202</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="I29">
-        <v>33.36561743341404</v>
+        <v>48.73039581777446</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         <v>2023</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="I30">
-        <v>33.321854912764</v>
+        <v>47.34752796824252</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         <v>2023</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="I31">
-        <v>33.3182503770739</v>
+        <v>45.62353365818444</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         <v>2023</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="I32">
-        <v>33.15344640511678</v>
+        <v>45.25951557093425</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         <v>2023</v>
       </c>
       <c r="B33">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I33">
-        <v>32.06073060978634</v>
+        <v>44.54673315432809</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1884,21 +1884,21 @@
         <v>2023</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I34">
-        <v>31.9854611540209</v>
+        <v>44.32121297206233</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         <v>2023</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="I35">
-        <v>31.9653520572216</v>
+        <v>44.11147011308562</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1976,21 +1976,21 @@
         <v>2023</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="I36">
-        <v>31.39742505403628</v>
+        <v>42.94783926123657</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="I37">
-        <v>31.35107602190246</v>
+        <v>42.66316926400247</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         <v>2023</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="I38">
-        <v>31.13412607083493</v>
+        <v>42.47900693683826</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         <v>2023</v>
       </c>
       <c r="B39">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="I39">
-        <v>30.96540550843419</v>
+        <v>42.42776486217203</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         <v>2023</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="I40">
-        <v>30.823264962068</v>
+        <v>41.67553757717692</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="I41">
-        <v>30.7475884244373</v>
+        <v>41.59894575005491</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I42">
-        <v>30.72921622736067</v>
+        <v>41.49421789409617</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         <v>2023</v>
       </c>
       <c r="B43">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="I43">
-        <v>30.66593404336172</v>
+        <v>41.35705905357841</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         <v>2023</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I44">
-        <v>30.6238260800064</v>
+        <v>41.09768661609066</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         <v>2023</v>
       </c>
       <c r="B45">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="I45">
-        <v>30.51222762188431</v>
+        <v>40.98448727419247</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2436,21 +2436,21 @@
         <v>2023</v>
       </c>
       <c r="B46">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I46">
-        <v>30.47210300429185</v>
+        <v>40.46981248712137</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         <v>2023</v>
       </c>
       <c r="B47">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="I47">
-        <v>30.44702569517775</v>
+        <v>39.99644791759169</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="I48">
-        <v>30.42711066871776</v>
+        <v>39.97377049180328</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         <v>2023</v>
       </c>
       <c r="B49">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="I49">
-        <v>30.29593216983934</v>
+        <v>39.93742989260849</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         <v>2023</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="I50">
-        <v>30.22235576923077</v>
+        <v>39.68501597206745</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         <v>2023</v>
       </c>
       <c r="B51">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="I51">
-        <v>30.19117198703689</v>
+        <v>39.62089077412514</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         <v>2023</v>
       </c>
       <c r="B52">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="I52">
-        <v>30.15543375867089</v>
+        <v>39.60848161385728</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         <v>2023</v>
       </c>
       <c r="B53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="I53">
-        <v>30.12302029350511</v>
+        <v>39.35233547231756</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2804,21 +2804,21 @@
         <v>2023</v>
       </c>
       <c r="B54">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="I54">
-        <v>29.87188426006624</v>
+        <v>39.30318754633061</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         <v>2023</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I55">
-        <v>29.71117622436166</v>
+        <v>39.23263048738334</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2896,21 +2896,21 @@
         <v>2023</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="I56">
-        <v>29.48140387637507</v>
+        <v>39.11948725774455</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         <v>2023</v>
       </c>
       <c r="B57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I57">
-        <v>29.47775053859297</v>
+        <v>39.0444648478489</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2988,21 +2988,21 @@
         <v>2023</v>
       </c>
       <c r="B58">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I58">
-        <v>29.33844678811122</v>
+        <v>38.70342451001508</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         <v>2023</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="I59">
-        <v>29.20956492859515</v>
+        <v>38.53563902732716</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         <v>2023</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="I60">
-        <v>29.18541400846149</v>
+        <v>38.45813026140895</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="I61">
-        <v>29.17214191852825</v>
+        <v>38.16784823161314</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3172,21 +3172,21 @@
         <v>2023</v>
       </c>
       <c r="B62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I62">
-        <v>29.00693683826214</v>
+        <v>37.93321871323862</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         <v>2023</v>
       </c>
       <c r="B63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="I63">
-        <v>28.99862924752904</v>
+        <v>37.88838920686835</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I64">
-        <v>28.98393791734344</v>
+        <v>37.80669514254495</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         <v>2023</v>
       </c>
       <c r="B65">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="I65">
-        <v>28.96435776731674</v>
+        <v>37.68886739997582</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         <v>2023</v>
       </c>
       <c r="B66">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="I66">
-        <v>28.93995552260934</v>
+        <v>37.61885468025658</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3411,12 +3411,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I67">
-        <v>28.9042675893887</v>
+        <v>37.33530093812585</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         <v>2023</v>
       </c>
       <c r="B68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="I68">
-        <v>28.90302613480055</v>
+        <v>37.01768488745981</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3503,12 +3503,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I69">
-        <v>28.84732020301976</v>
+        <v>36.73091750192752</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         <v>2023</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I70">
-        <v>28.83402894947163</v>
+        <v>36.68062324112842</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3586,21 +3586,21 @@
         <v>2023</v>
       </c>
       <c r="B71">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="I71">
-        <v>28.78717830174141</v>
+        <v>36.48783899480279</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         <v>2023</v>
       </c>
       <c r="B72">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="I72">
-        <v>28.76666337513577</v>
+        <v>36.44416323948118</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I73">
-        <v>28.76100819921045</v>
+        <v>36.27546569507876</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         <v>2023</v>
       </c>
       <c r="B74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="I74">
-        <v>28.70522125965816</v>
+        <v>35.91801357880038</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         <v>2023</v>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="I75">
-        <v>28.67298578199052</v>
+        <v>35.90742504256485</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         <v>2023</v>
       </c>
       <c r="B76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I76">
-        <v>28.62020905923345</v>
+        <v>35.89406651167492</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         <v>2023</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="I77">
-        <v>28.6020846106683</v>
+        <v>35.79242671109532</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         <v>2023</v>
       </c>
       <c r="B78">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I78">
-        <v>28.58309817317689</v>
+        <v>35.74922760041195</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         <v>2023</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="I79">
-        <v>28.56509417593645</v>
+        <v>35.67816091954023</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         <v>2023</v>
       </c>
       <c r="B80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I80">
-        <v>28.55013838620396</v>
+        <v>35.66784026390079</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         <v>2023</v>
       </c>
       <c r="B81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="I81">
-        <v>28.54551275210757</v>
+        <v>35.65217391304348</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         <v>2023</v>
       </c>
       <c r="B82">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I82">
-        <v>28.54175742900275</v>
+        <v>35.57784302728383</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4138,21 +4138,21 @@
         <v>2023</v>
       </c>
       <c r="B83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="I83">
-        <v>28.45131012905749</v>
+        <v>35.47109505280712</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         <v>2023</v>
       </c>
       <c r="B84">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I84">
-        <v>28.4129323047586</v>
+        <v>35.39836646632763</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4230,21 +4230,21 @@
         <v>2023</v>
       </c>
       <c r="B85">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="I85">
-        <v>28.34814587802635</v>
+        <v>35.26105495422966</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="I86">
-        <v>28.33602584814216</v>
+        <v>35.16930990141449</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         <v>2023</v>
       </c>
       <c r="B87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="I87">
-        <v>28.32943756673304</v>
+        <v>35.16519463526333</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         <v>2023</v>
       </c>
       <c r="B88">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I88">
-        <v>28.2897550782866</v>
+        <v>35.09230605058158</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4414,21 +4414,21 @@
         <v>2023</v>
       </c>
       <c r="B89">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="I89">
-        <v>28.22055873575028</v>
+        <v>35.03923250420915</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4460,21 +4460,21 @@
         <v>2023</v>
       </c>
       <c r="B90">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I90">
-        <v>28.1533688282836</v>
+        <v>35.02410061608197</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         <v>2023</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="I91">
-        <v>28.15070860698237</v>
+        <v>34.97151486031986</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4552,21 +4552,21 @@
         <v>2023</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="I92">
-        <v>28.11441112276767</v>
+        <v>34.9469918333708</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         <v>2023</v>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I93">
-        <v>28.08205271817132</v>
+        <v>34.67736028711638</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         <v>2023</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I94">
-        <v>28.02662092188443</v>
+        <v>34.4320404172099</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         <v>2023</v>
       </c>
       <c r="B95">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Ránquil</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I95">
-        <v>27.97467313543294</v>
+        <v>34.23672566371682</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4736,21 +4736,21 @@
         <v>2023</v>
       </c>
       <c r="B96">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I96">
-        <v>27.96825215118387</v>
+        <v>34.18774966711052</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         <v>2023</v>
       </c>
       <c r="B97">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="I97">
-        <v>27.94965593388577</v>
+        <v>34.16579951439473</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         <v>2023</v>
       </c>
       <c r="B98">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="I98">
-        <v>27.90201866595104</v>
+        <v>33.91051179895801</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         <v>2023</v>
       </c>
       <c r="B99">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="I99">
-        <v>27.82276475795555</v>
+        <v>33.90350877192982</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         <v>2023</v>
       </c>
       <c r="B100">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I100">
-        <v>27.77868318122556</v>
+        <v>33.80997177798683</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         <v>2023</v>
       </c>
       <c r="B101">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I101">
-        <v>27.74411443329691</v>
+        <v>33.70034843205575</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         <v>2023</v>
       </c>
       <c r="B102">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I102">
-        <v>27.74338773213281</v>
+        <v>33.58485111303845</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I103">
-        <v>27.69215634837356</v>
+        <v>33.53707414829659</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5113,12 +5113,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I104">
-        <v>27.67238306467583</v>
+        <v>33.44643372798151</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5150,21 +5150,21 @@
         <v>2023</v>
       </c>
       <c r="B105">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="I105">
-        <v>27.64575347992738</v>
+        <v>33.3182503770739</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         <v>2023</v>
       </c>
       <c r="B106">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="I106">
-        <v>27.584875667083</v>
+        <v>33.31038890800924</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         <v>2023</v>
       </c>
       <c r="B107">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="I107">
-        <v>27.55531749843005</v>
+        <v>33.24736359468134</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5288,21 +5288,21 @@
         <v>2023</v>
       </c>
       <c r="B108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I108">
-        <v>27.53105909808497</v>
+        <v>32.99845336561092</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5343,12 +5343,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="I109">
-        <v>27.51733131992587</v>
+        <v>32.89264939185616</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5389,12 +5389,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I110">
-        <v>27.48987854251012</v>
+        <v>32.38318737717742</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         <v>2023</v>
       </c>
       <c r="B111">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>La Pintana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="I111">
-        <v>27.4742995363838</v>
+        <v>32.06073060978634</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="I112">
-        <v>27.42341047878072</v>
+        <v>32.0533832826036</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5518,21 +5518,21 @@
         <v>2023</v>
       </c>
       <c r="B113">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="I113">
-        <v>27.40592389585749</v>
+        <v>31.9653520572216</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5573,12 +5573,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="I114">
-        <v>27.40398498411782</v>
+        <v>31.94270401573133</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5610,21 +5610,21 @@
         <v>2023</v>
       </c>
       <c r="B115">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="I115">
-        <v>27.39553520320549</v>
+        <v>31.81333849953988</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="I116">
-        <v>27.29648991784914</v>
+        <v>31.0788476849953</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -5702,21 +5702,21 @@
         <v>2023</v>
       </c>
       <c r="B117">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I117">
-        <v>27.28896297178235</v>
+        <v>30.98179039857379</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         <v>2023</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="I118">
-        <v>27.19967030702658</v>
+        <v>30.96540550843419</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5794,21 +5794,21 @@
         <v>2023</v>
       </c>
       <c r="B119">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="I119">
-        <v>27.17278706164829</v>
+        <v>30.84421500151837</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         <v>2023</v>
       </c>
       <c r="B120">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I120">
-        <v>27.17205105315222</v>
+        <v>30.66593404336172</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5886,21 +5886,21 @@
         <v>2023</v>
       </c>
       <c r="B121">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="I121">
-        <v>27.12409886714727</v>
+        <v>30.6238260800064</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -5932,21 +5932,21 @@
         <v>2023</v>
       </c>
       <c r="B122">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I122">
-        <v>27.09688716477418</v>
+        <v>30.54745375762941</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -5987,12 +5987,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I123">
-        <v>27.08032178995663</v>
+        <v>30.51222762188431</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I124">
-        <v>27.06691464736342</v>
+        <v>30.47210300429185</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6070,21 +6070,21 @@
         <v>2023</v>
       </c>
       <c r="B125">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="I125">
-        <v>27.05221168908771</v>
+        <v>30.44702569517775</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6125,12 +6125,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="I126">
-        <v>27.0404984423676</v>
+        <v>30.40264423076923</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         <v>2023</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I127">
-        <v>27.01269223642764</v>
+        <v>30.19117198703689</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         <v>2023</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="I128">
-        <v>27.00722749397709</v>
+        <v>30.15543375867089</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         <v>2023</v>
       </c>
       <c r="B129">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="I129">
-        <v>27.00158646218932</v>
+        <v>29.87188426006624</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         <v>2023</v>
       </c>
       <c r="B130">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="I130">
-        <v>26.99526934228598</v>
+        <v>29.33844678811122</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6355,12 +6355,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="I131">
-        <v>26.96813830547221</v>
+        <v>29.14199793252514</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         <v>2023</v>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I132">
-        <v>26.82531559194814</v>
+        <v>29.00376726663876</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         <v>2023</v>
       </c>
       <c r="B133">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="I133">
-        <v>26.81550539744848</v>
+        <v>28.96435776731674</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         <v>2023</v>
       </c>
       <c r="B134">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="I134">
-        <v>26.80141953402252</v>
+        <v>28.76666337513577</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I135">
-        <v>26.7682437850842</v>
+        <v>28.67298578199052</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         <v>2023</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="I136">
-        <v>26.72102466975908</v>
+        <v>28.58309817317689</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         <v>2023</v>
       </c>
       <c r="B137">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="I137">
-        <v>26.7152342309111</v>
+        <v>28.54175742900275</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         <v>2023</v>
       </c>
       <c r="B138">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="I138">
-        <v>26.62068965517241</v>
+        <v>28.4129323047586</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6714,21 +6714,21 @@
         <v>2023</v>
       </c>
       <c r="B139">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="I139">
-        <v>26.56415694591728</v>
+        <v>28.2897550782866</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         <v>2023</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="I140">
-        <v>26.55094118508753</v>
+        <v>28.22055873575028</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I141">
-        <v>26.30363744180472</v>
+        <v>28.1533688282836</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -6852,21 +6852,21 @@
         <v>2023</v>
       </c>
       <c r="B142">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I142">
-        <v>26.20073228516046</v>
+        <v>28.08205271817132</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -6898,21 +6898,21 @@
         <v>2023</v>
       </c>
       <c r="B143">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I143">
-        <v>26.18054030309686</v>
+        <v>27.94965593388577</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -6944,21 +6944,21 @@
         <v>2023</v>
       </c>
       <c r="B144">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I144">
-        <v>26.13864030987044</v>
+        <v>27.83568362967505</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -6990,21 +6990,21 @@
         <v>2023</v>
       </c>
       <c r="B145">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="I145">
-        <v>26.12190743775853</v>
+        <v>27.74338773213281</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         <v>2023</v>
       </c>
       <c r="B146">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I146">
-        <v>25.89897711694611</v>
+        <v>27.584875667083</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         <v>2023</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="I147">
-        <v>25.88852459016394</v>
+        <v>27.55531749843005</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I148">
-        <v>25.88376273217495</v>
+        <v>27.4742995363838</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7174,21 +7174,21 @@
         <v>2023</v>
       </c>
       <c r="B149">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="I149">
-        <v>25.86076903744659</v>
+        <v>27.39553520320549</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I150">
-        <v>25.82824059183017</v>
+        <v>27.28896297178235</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         <v>2023</v>
       </c>
       <c r="B151">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I151">
-        <v>25.80925483380404</v>
+        <v>27.17278706164829</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7321,12 +7321,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I152">
-        <v>25.75039758935297</v>
+        <v>27.09688716477418</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7367,12 +7367,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I153">
-        <v>25.72203087720602</v>
+        <v>27.08032178995663</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="I154">
-        <v>25.6521016780196</v>
+        <v>27.06691464736342</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="I155">
-        <v>25.59936888284567</v>
+        <v>27.05221168908771</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -7496,21 +7496,21 @@
         <v>2023</v>
       </c>
       <c r="B156">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="I156">
-        <v>25.59935503033903</v>
+        <v>26.8659379879545</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         <v>2023</v>
       </c>
       <c r="B157">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="I157">
-        <v>25.58211256746338</v>
+        <v>26.7682437850842</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -7588,21 +7588,21 @@
         <v>2023</v>
       </c>
       <c r="B158">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="I158">
-        <v>25.33475349969568</v>
+        <v>26.7152342309111</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -7634,21 +7634,21 @@
         <v>2023</v>
       </c>
       <c r="B159">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I159">
-        <v>25.23310283292438</v>
+        <v>26.30363744180472</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -7680,21 +7680,21 @@
         <v>2023</v>
       </c>
       <c r="B160">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I160">
-        <v>25.20578916362826</v>
+        <v>26.24412476855149</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         <v>2023</v>
       </c>
       <c r="B161">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="I161">
-        <v>25.17171780388966</v>
+        <v>26.13864030987044</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -7772,21 +7772,21 @@
         <v>2023</v>
       </c>
       <c r="B162">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="I162">
-        <v>25.16353229762878</v>
+        <v>25.88376273217495</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -7818,21 +7818,21 @@
         <v>2023</v>
       </c>
       <c r="B163">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I163">
-        <v>25.14741588622962</v>
+        <v>25.82824059183017</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="I164">
-        <v>25.08145580589255</v>
+        <v>25.80925483380404</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -7910,21 +7910,21 @@
         <v>2023</v>
       </c>
       <c r="B165">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="I165">
-        <v>25.05733944954128</v>
+        <v>25.76076286635816</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="I166">
-        <v>24.83400514730942</v>
+        <v>25.75039758935297</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -8002,21 +8002,21 @@
         <v>2023</v>
       </c>
       <c r="B167">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I167">
-        <v>24.82858173944425</v>
+        <v>25.72203087720602</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8048,21 +8048,21 @@
         <v>2023</v>
       </c>
       <c r="B168">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="I168">
-        <v>24.80696335813562</v>
+        <v>25.6521016780196</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8094,21 +8094,21 @@
         <v>2023</v>
       </c>
       <c r="B169">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I169">
-        <v>24.79807201528075</v>
+        <v>25.59936888284567</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -8140,21 +8140,21 @@
         <v>2023</v>
       </c>
       <c r="B170">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="I170">
-        <v>24.76178709866724</v>
+        <v>25.59935503033903</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -8195,12 +8195,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I171">
-        <v>24.75319473245777</v>
+        <v>25.20578916362826</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="I172">
-        <v>24.70674666340149</v>
+        <v>25.17171780388966</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8278,21 +8278,21 @@
         <v>2023</v>
       </c>
       <c r="B173">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I173">
-        <v>24.69725725185692</v>
+        <v>25.08145580589255</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -8324,21 +8324,21 @@
         <v>2023</v>
       </c>
       <c r="B174">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="I174">
-        <v>24.59919839679359</v>
+        <v>25.05733944954128</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="I175">
-        <v>24.55055726225531</v>
+        <v>24.83400514730942</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         <v>2023</v>
       </c>
       <c r="B176">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="I176">
-        <v>24.4288649824731</v>
+        <v>24.76178709866724</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -8462,21 +8462,21 @@
         <v>2023</v>
       </c>
       <c r="B177">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="I177">
-        <v>24.39396507882692</v>
+        <v>24.75319473245777</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -8508,21 +8508,21 @@
         <v>2023</v>
       </c>
       <c r="B178">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I178">
-        <v>24.31947352677236</v>
+        <v>24.70674666340149</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -8554,21 +8554,21 @@
         <v>2023</v>
       </c>
       <c r="B179">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="I179">
-        <v>24.22087308470656</v>
+        <v>24.55055726225531</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         <v>2023</v>
       </c>
       <c r="B180">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Ninhue</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I180">
-        <v>24.14770710374237</v>
+        <v>24.31947352677236</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -8830,21 +8830,21 @@
         <v>2023</v>
       </c>
       <c r="B185">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="I185">
-        <v>22.57871959409044</v>
+        <v>22.50593237097093</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -8876,21 +8876,21 @@
         <v>2023</v>
       </c>
       <c r="B186">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I186">
-        <v>22.50593237097093</v>
+        <v>21.05248129747016</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -8922,21 +8922,21 @@
         <v>2023</v>
       </c>
       <c r="B187">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="I187">
-        <v>20.6620319907376</v>
+        <v>20.67263544536272</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="I188">
-        <v>20.47803074855079</v>
+        <v>20.6620319907376</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9014,21 +9014,21 @@
         <v>2023</v>
       </c>
       <c r="B189">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="I189">
-        <v>20.01121862291404</v>
+        <v>20.47803074855079</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -9198,21 +9198,21 @@
         <v>2023</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="I193">
-        <v>48.20271066588096</v>
+        <v>49.47596073864581</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -9244,21 +9244,21 @@
         <v>2023</v>
       </c>
       <c r="B194">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Camiña</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="I194">
-        <v>45.13788098693759</v>
+        <v>49.41060903732809</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9290,21 +9290,21 @@
         <v>2023</v>
       </c>
       <c r="B195">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>General Lagos</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="I195">
-        <v>39.21568627450981</v>
+        <v>44.92035024791645</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -9336,21 +9336,21 @@
         <v>2023</v>
       </c>
       <c r="B196">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Alto del Carmen</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="I196">
-        <v>39.16243654822335</v>
+        <v>44.03973509933775</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -9382,21 +9382,21 @@
         <v>2023</v>
       </c>
       <c r="B197">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="I197">
-        <v>38.76187126275062</v>
+        <v>40.63860667634253</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         <v>2023</v>
       </c>
       <c r="B198">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sierra Gorda</t>
+          <t>General Lagos</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="I198">
-        <v>36.9542066027689</v>
+        <v>39.21568627450981</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -9474,21 +9474,21 @@
         <v>2023</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="I199">
-        <v>36.67572964496441</v>
+        <v>38.17379182156134</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -9520,21 +9520,21 @@
         <v>2023</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="I200">
-        <v>35.79692626489381</v>
+        <v>37.79017961825259</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -9566,21 +9566,21 @@
         <v>2023</v>
       </c>
       <c r="B201">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="I201">
-        <v>34.50520833333333</v>
+        <v>37.38823825714645</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -9612,21 +9612,21 @@
         <v>2023</v>
       </c>
       <c r="B202">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="I202">
-        <v>34.31589290100712</v>
+        <v>36.59891427850019</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -9658,21 +9658,21 @@
         <v>2023</v>
       </c>
       <c r="B203">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="I203">
-        <v>33.92330383480826</v>
+        <v>36.29968343299332</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -9704,21 +9704,21 @@
         <v>2023</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Huasco</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="I204">
-        <v>32.40209832865683</v>
+        <v>36.06220280169644</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         <v>2023</v>
       </c>
       <c r="B205">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Freirina</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I205">
-        <v>30.77715557016268</v>
+        <v>36.05778745299822</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         <v>2023</v>
       </c>
       <c r="B206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="I206">
-        <v>30.67484662576687</v>
+        <v>35.71065989847716</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -9842,21 +9842,21 @@
         <v>2023</v>
       </c>
       <c r="B207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="I207">
-        <v>30.57240542627109</v>
+        <v>35.52851935769875</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -9888,21 +9888,21 @@
         <v>2023</v>
       </c>
       <c r="B208">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Calama</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="I208">
-        <v>30.34142404344938</v>
+        <v>34.50520833333333</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -9934,21 +9934,21 @@
         <v>2023</v>
       </c>
       <c r="B209">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Diego de Almagro</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="I209">
-        <v>29.92242756103126</v>
+        <v>34.35695799323113</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9980,21 +9980,21 @@
         <v>2023</v>
       </c>
       <c r="B210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I210">
-        <v>29.74976070012307</v>
+        <v>34.34106098579782</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10026,21 +10026,21 @@
         <v>2023</v>
       </c>
       <c r="B211">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I211">
-        <v>29.5693135935397</v>
+        <v>33.92330383480826</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -10072,21 +10072,21 @@
         <v>2023</v>
       </c>
       <c r="B212">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="I212">
-        <v>29.43941980040454</v>
+        <v>33.7267012242197</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         <v>2023</v>
       </c>
       <c r="B213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="I213">
-        <v>29.43441484661027</v>
+        <v>33.63052099001778</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -10164,21 +10164,21 @@
         <v>2023</v>
       </c>
       <c r="B214">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="I214">
-        <v>29.36657851655963</v>
+        <v>32.8815556865056</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="I215">
-        <v>29.32329830791451</v>
+        <v>32.85322450277597</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10256,21 +10256,21 @@
         <v>2023</v>
       </c>
       <c r="B216">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="I216">
-        <v>29.28995121266365</v>
+        <v>32.066609735269</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -10302,21 +10302,21 @@
         <v>2023</v>
       </c>
       <c r="B217">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>Caldera</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="I217">
-        <v>29.25381070542361</v>
+        <v>31.78988599006784</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -10348,21 +10348,21 @@
         <v>2023</v>
       </c>
       <c r="B218">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="I218">
-        <v>29.25327553935573</v>
+        <v>31.65502288605155</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -10394,21 +10394,21 @@
         <v>2023</v>
       </c>
       <c r="B219">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="I219">
-        <v>29.1014213442544</v>
+        <v>30.77715557016268</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         <v>2023</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Alto del Carmen</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="I220">
-        <v>29.03973509933775</v>
+        <v>30.13004683143719</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -10486,21 +10486,21 @@
         <v>2023</v>
       </c>
       <c r="B221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Huasco</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I221">
-        <v>29.03225806451613</v>
+        <v>29.98318474570894</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -10532,21 +10532,21 @@
         <v>2023</v>
       </c>
       <c r="B222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="I222">
-        <v>28.81566677028287</v>
+        <v>27.14522045601669</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -10578,21 +10578,21 @@
         <v>2023</v>
       </c>
       <c r="B223">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="I223">
-        <v>28.57477840829152</v>
+        <v>26.06349373486364</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -10633,12 +10633,12 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Tierra Amarilla</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="I224">
-        <v>28.4395327691124</v>
+        <v>25.92729059199214</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -10670,21 +10670,21 @@
         <v>2023</v>
       </c>
       <c r="B225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>Diego de Almagro</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="I225">
-        <v>28.34645669291339</v>
+        <v>24.1843486196669</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -10716,21 +10716,21 @@
         <v>2023</v>
       </c>
       <c r="B226">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Colchane</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I226">
-        <v>28.18426980551413</v>
+        <v>24.14553472987872</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         <v>2023</v>
       </c>
       <c r="B227">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="I227">
-        <v>27.7516708437761</v>
+        <v>24.12185265775567</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -10808,21 +10808,21 @@
         <v>2023</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Ollagüe</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="I228">
-        <v>27.69402287276128</v>
+        <v>23.62204724409449</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -10854,21 +10854,21 @@
         <v>2023</v>
       </c>
       <c r="B229">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I229">
-        <v>27.66031598513011</v>
+        <v>23.4070108789501</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="I230">
-        <v>27.36574989737657</v>
+        <v>22.75814456842184</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -10946,21 +10946,21 @@
         <v>2023</v>
       </c>
       <c r="B231">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="I231">
-        <v>27.14015528568585</v>
+        <v>21.35767458348104</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -10992,21 +10992,21 @@
         <v>2023</v>
       </c>
       <c r="B232">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="I232">
-        <v>26.00232906338379</v>
+        <v>20.63425338187199</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11038,21 +11038,21 @@
         <v>2023</v>
       </c>
       <c r="B233">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -11071,7 +11071,7 @@
         </is>
       </c>
       <c r="I233">
-        <v>22.96655765376094</v>
+        <v>17.56393001345895</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -11084,21 +11084,21 @@
         <v>2023</v>
       </c>
       <c r="B234">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="I234">
-        <v>22.29862475442043</v>
+        <v>15.39164476133531</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -11130,21 +11130,21 @@
         <v>2023</v>
       </c>
       <c r="B235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Sierra Gorda</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="I235">
-        <v>21.16868798235943</v>
+        <v>15.33546325878594</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11176,21 +11176,21 @@
         <v>2023</v>
       </c>
       <c r="B236">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="I236">
-        <v>37.85622357050929</v>
+        <v>50.50732807215332</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -11231,12 +11231,12 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I237">
-        <v>36.76562175627984</v>
+        <v>46.77833310819938</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -11268,21 +11268,21 @@
         <v>2023</v>
       </c>
       <c r="B238">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="I238">
-        <v>34.5697851860547</v>
+        <v>45.2066467831274</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -11314,21 +11314,21 @@
         <v>2023</v>
       </c>
       <c r="B239">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="I239">
-        <v>33.9924670433145</v>
+        <v>45.14980096375445</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -11369,12 +11369,12 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="I240">
-        <v>33.52737352737353</v>
+        <v>44.86350574712644</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -11406,21 +11406,21 @@
         <v>2023</v>
       </c>
       <c r="B241">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="I241">
-        <v>32.88755458515284</v>
+        <v>42.56713554987212</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -11452,21 +11452,21 @@
         <v>2023</v>
       </c>
       <c r="B242">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="I242">
-        <v>32.8234658988663</v>
+        <v>40.51179793951479</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -11498,21 +11498,21 @@
         <v>2023</v>
       </c>
       <c r="B243">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="I243">
-        <v>32.71940667490729</v>
+        <v>40.43387349712494</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -11544,21 +11544,21 @@
         <v>2023</v>
       </c>
       <c r="B244">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="I244">
-        <v>32.00025554206862</v>
+        <v>39.61114437673911</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -11599,12 +11599,12 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="I245">
-        <v>31.79620343839542</v>
+        <v>39.1516975453776</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -11645,12 +11645,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I246">
-        <v>31.33427082471669</v>
+        <v>37.85622357050929</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="I247">
-        <v>31.19116354964228</v>
+        <v>37.82996712071395</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -11728,21 +11728,21 @@
         <v>2023</v>
       </c>
       <c r="B248">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="I248">
-        <v>31.16888744448055</v>
+        <v>37.25377334356612</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -11774,21 +11774,21 @@
         <v>2023</v>
       </c>
       <c r="B249">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="I249">
-        <v>31.16040032458751</v>
+        <v>36.8324421825678</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -11820,21 +11820,21 @@
         <v>2023</v>
       </c>
       <c r="B250">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="I250">
-        <v>31.06972518737224</v>
+        <v>36.69429097605893</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -11866,21 +11866,21 @@
         <v>2023</v>
       </c>
       <c r="B251">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="I251">
-        <v>31.02894477497536</v>
+        <v>36.52335675899132</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -11912,21 +11912,21 @@
         <v>2023</v>
       </c>
       <c r="B252">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Hualpén</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I252">
-        <v>31.00607279619387</v>
+        <v>35.83060247038064</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -11958,21 +11958,21 @@
         <v>2023</v>
       </c>
       <c r="B253">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="I253">
-        <v>30.93306288032454</v>
+        <v>35.75220352564102</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -12004,21 +12004,21 @@
         <v>2023</v>
       </c>
       <c r="B254">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="I254">
-        <v>30.73514784338548</v>
+        <v>35.43320878094349</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -12059,12 +12059,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="I255">
-        <v>30.59195661997289</v>
+        <v>35.04997101856569</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -12096,21 +12096,21 @@
         <v>2023</v>
       </c>
       <c r="B256">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="I256">
-        <v>30.54762788435696</v>
+        <v>34.5697851860547</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -12142,21 +12142,21 @@
         <v>2023</v>
       </c>
       <c r="B257">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="I257">
-        <v>30.33754920847642</v>
+        <v>34.38579181055748</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -12188,21 +12188,21 @@
         <v>2023</v>
       </c>
       <c r="B258">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="I258">
-        <v>30.22203947368421</v>
+        <v>34.18961628377313</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -12234,21 +12234,21 @@
         <v>2023</v>
       </c>
       <c r="B259">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -12267,7 +12267,7 @@
         </is>
       </c>
       <c r="I259">
-        <v>30.21960013110456</v>
+        <v>33.9924670433145</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -12280,21 +12280,21 @@
         <v>2023</v>
       </c>
       <c r="B260">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="I260">
-        <v>30.1460883811951</v>
+        <v>33.51747058295159</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -12326,21 +12326,21 @@
         <v>2023</v>
       </c>
       <c r="B261">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="I261">
-        <v>29.64576407199358</v>
+        <v>33.376611747851</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -12372,21 +12372,21 @@
         <v>2023</v>
       </c>
       <c r="B262">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="I262">
-        <v>29.63632710468154</v>
+        <v>33.18507890961263</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -12418,21 +12418,21 @@
         <v>2023</v>
       </c>
       <c r="B263">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I263">
-        <v>29.62615176947004</v>
+        <v>32.88755458515284</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -12473,12 +12473,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="I264">
-        <v>29.57406449387825</v>
+        <v>32.8234658988663</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -12519,12 +12519,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="I265">
-        <v>29.52029520295203</v>
+        <v>32.71940667490729</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -12556,21 +12556,21 @@
         <v>2023</v>
       </c>
       <c r="B266">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="I266">
-        <v>29.47914154810706</v>
+        <v>32.00025554206862</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         <v>2023</v>
       </c>
       <c r="B267">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="I267">
-        <v>29.47588126159555</v>
+        <v>31.88567404190387</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -12657,12 +12657,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="I268">
-        <v>29.22785309619776</v>
+        <v>31.57215772056761</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         <v>2023</v>
       </c>
       <c r="B269">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="I269">
-        <v>29.18372075063711</v>
+        <v>31.41010101010101</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -12749,12 +12749,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="I270">
-        <v>29.13669064748202</v>
+        <v>31.33427082471669</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -12795,12 +12795,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="I271">
-        <v>29.13448207565855</v>
+        <v>31.16888744448055</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -12832,21 +12832,21 @@
         <v>2023</v>
       </c>
       <c r="B272">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="I272">
-        <v>29.11217247690042</v>
+        <v>31.16040032458751</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -12887,12 +12887,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="I273">
-        <v>29.0653115628124</v>
+        <v>31.06972518737224</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -12924,21 +12924,21 @@
         <v>2023</v>
       </c>
       <c r="B274">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="I274">
-        <v>29.0115211220571</v>
+        <v>31.02894477497536</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -12970,21 +12970,21 @@
         <v>2023</v>
       </c>
       <c r="B275">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="I275">
-        <v>28.96959459459459</v>
+        <v>31.00607279619387</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -13016,21 +13016,21 @@
         <v>2023</v>
       </c>
       <c r="B276">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="I276">
-        <v>28.91705544775195</v>
+        <v>30.93306288032454</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         <v>2023</v>
       </c>
       <c r="B277">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Futrono</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -13095,7 +13095,7 @@
         </is>
       </c>
       <c r="I277">
-        <v>28.89420831387202</v>
+        <v>30.73514784338548</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -13108,21 +13108,21 @@
         <v>2023</v>
       </c>
       <c r="B278">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="I278">
-        <v>28.85380996130182</v>
+        <v>30.52075201249088</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         <v>2023</v>
       </c>
       <c r="B279">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="I279">
-        <v>28.80741337630943</v>
+        <v>30.33754920847642</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -13200,21 +13200,21 @@
         <v>2023</v>
       </c>
       <c r="B280">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Los Ángeles</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -13233,7 +13233,7 @@
         </is>
       </c>
       <c r="I280">
-        <v>28.78201240845267</v>
+        <v>30.29890921390118</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -13255,12 +13255,12 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="I281">
-        <v>28.77197341449779</v>
+        <v>30.22203947368421</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -13292,21 +13292,21 @@
         <v>2023</v>
       </c>
       <c r="B282">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="I282">
-        <v>28.60646854144088</v>
+        <v>30.21960013110456</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -13338,21 +13338,21 @@
         <v>2023</v>
       </c>
       <c r="B283">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="I283">
-        <v>28.41438106455774</v>
+        <v>30.1460883811951</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -13384,21 +13384,21 @@
         <v>2023</v>
       </c>
       <c r="B284">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="I284">
-        <v>28.37279218338971</v>
+        <v>29.64576407199358</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -13439,12 +13439,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -13463,7 +13463,7 @@
         </is>
       </c>
       <c r="I285">
-        <v>28.34685234369392</v>
+        <v>29.63632710468154</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -13476,21 +13476,21 @@
         <v>2023</v>
       </c>
       <c r="B286">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="I286">
-        <v>28.32727272727273</v>
+        <v>29.57406449387825</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -13531,12 +13531,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="I287">
-        <v>28.30508474576271</v>
+        <v>29.52029520295203</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -13568,21 +13568,21 @@
         <v>2023</v>
       </c>
       <c r="B288">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I288">
-        <v>28.27265074187099</v>
+        <v>29.47914154810706</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -13623,12 +13623,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -13647,7 +13647,7 @@
         </is>
       </c>
       <c r="I289">
-        <v>28.15997987674506</v>
+        <v>29.47588126159555</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -13660,21 +13660,21 @@
         <v>2023</v>
       </c>
       <c r="B290">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -13693,7 +13693,7 @@
         </is>
       </c>
       <c r="I290">
-        <v>27.97514521140078</v>
+        <v>29.18372075063711</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -13706,21 +13706,21 @@
         <v>2023</v>
       </c>
       <c r="B291">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I291">
-        <v>27.97124971017853</v>
+        <v>29.13669064748202</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -13761,12 +13761,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="I292">
-        <v>27.95733678086619</v>
+        <v>29.13448207565855</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -13798,21 +13798,21 @@
         <v>2023</v>
       </c>
       <c r="B293">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="I293">
-        <v>27.95576684580405</v>
+        <v>29.11217247690042</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -13844,21 +13844,21 @@
         <v>2023</v>
       </c>
       <c r="B294">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="I294">
-        <v>27.94832437963673</v>
+        <v>29.0653115628124</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -13890,21 +13890,21 @@
         <v>2023</v>
       </c>
       <c r="B295">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="I295">
-        <v>27.86802889734671</v>
+        <v>29.0115211220571</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         <v>2023</v>
       </c>
       <c r="B296">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="I296">
-        <v>27.86760082637205</v>
+        <v>28.96959459459459</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -13982,21 +13982,21 @@
         <v>2023</v>
       </c>
       <c r="B297">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -14015,7 +14015,7 @@
         </is>
       </c>
       <c r="I297">
-        <v>27.81951121794872</v>
+        <v>28.91705544775195</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -14028,21 +14028,21 @@
         <v>2023</v>
       </c>
       <c r="B298">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="I298">
-        <v>27.77221108884436</v>
+        <v>28.85380996130182</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         <v>2023</v>
       </c>
       <c r="B299">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Lago Ranco</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="I299">
-        <v>27.74505494505495</v>
+        <v>28.80741337630943</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -14120,21 +14120,21 @@
         <v>2023</v>
       </c>
       <c r="B300">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="I300">
-        <v>27.73626232042775</v>
+        <v>28.78201240845267</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -14166,21 +14166,21 @@
         <v>2023</v>
       </c>
       <c r="B301">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I301">
-        <v>27.67084106369821</v>
+        <v>28.77197341449779</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -14212,21 +14212,21 @@
         <v>2023</v>
       </c>
       <c r="B302">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="I302">
-        <v>27.40115223739247</v>
+        <v>28.60646854144088</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -14258,21 +14258,21 @@
         <v>2023</v>
       </c>
       <c r="B303">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Los Álamos</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -14291,7 +14291,7 @@
         </is>
       </c>
       <c r="I303">
-        <v>27.3234046093685</v>
+        <v>28.4611522530438</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -14304,21 +14304,21 @@
         <v>2023</v>
       </c>
       <c r="B304">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="I304">
-        <v>27.19068676112264</v>
+        <v>28.34685234369392</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -14350,21 +14350,21 @@
         <v>2023</v>
       </c>
       <c r="B305">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -14383,7 +14383,7 @@
         </is>
       </c>
       <c r="I305">
-        <v>27.07374354156881</v>
+        <v>28.30508474576271</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -14396,21 +14396,21 @@
         <v>2023</v>
       </c>
       <c r="B306">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="I306">
-        <v>27.05787105513086</v>
+        <v>28.27265074187099</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -14442,21 +14442,21 @@
         <v>2023</v>
       </c>
       <c r="B307">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="I307">
-        <v>26.94163643408122</v>
+        <v>28.15997987674506</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="I308">
-        <v>26.80860983759422</v>
+        <v>27.97124971017853</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -14534,21 +14534,21 @@
         <v>2023</v>
       </c>
       <c r="B309">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="I309">
-        <v>26.80057388809182</v>
+        <v>27.95733678086619</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -14580,21 +14580,21 @@
         <v>2023</v>
       </c>
       <c r="B310">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="I310">
-        <v>26.76572933320794</v>
+        <v>27.86802889734671</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -14626,21 +14626,21 @@
         <v>2023</v>
       </c>
       <c r="B311">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="I311">
-        <v>26.66240409207161</v>
+        <v>27.77221108884436</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -14672,21 +14672,21 @@
         <v>2023</v>
       </c>
       <c r="B312">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="I312">
-        <v>26.65688944758712</v>
+        <v>27.74505494505495</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -14718,21 +14718,21 @@
         <v>2023</v>
       </c>
       <c r="B313">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -14751,7 +14751,7 @@
         </is>
       </c>
       <c r="I313">
-        <v>26.39027362357372</v>
+        <v>27.67084106369821</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -14764,21 +14764,21 @@
         <v>2023</v>
       </c>
       <c r="B314">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="I314">
-        <v>26.35040947900331</v>
+        <v>27.40115223739247</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -14810,21 +14810,21 @@
         <v>2023</v>
       </c>
       <c r="B315">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="I315">
-        <v>26.32902298850574</v>
+        <v>27.3234046093685</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -14865,12 +14865,12 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -14889,7 +14889,7 @@
         </is>
       </c>
       <c r="I316">
-        <v>26.2898049864231</v>
+        <v>27.19068676112264</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -14902,21 +14902,21 @@
         <v>2023</v>
       </c>
       <c r="B317">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="I317">
-        <v>26.17168228909719</v>
+        <v>27.05787105513086</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -14948,21 +14948,21 @@
         <v>2023</v>
       </c>
       <c r="B318">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="I318">
-        <v>26.10619469026549</v>
+        <v>26.80860983759422</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="I319">
-        <v>26.01289134438305</v>
+        <v>26.37560637560637</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -15049,12 +15049,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="I320">
-        <v>25.73802949454413</v>
+        <v>26.2898049864231</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -15086,21 +15086,21 @@
         <v>2023</v>
       </c>
       <c r="B321">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="I321">
-        <v>25.49399457574584</v>
+        <v>26.10619469026549</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -15132,21 +15132,21 @@
         <v>2023</v>
       </c>
       <c r="B322">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="I322">
-        <v>25.35543337070055</v>
+        <v>25.73802949454413</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -15178,21 +15178,21 @@
         <v>2023</v>
       </c>
       <c r="B323">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="I323">
-        <v>25.28644804425129</v>
+        <v>25.51739719837325</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -15233,12 +15233,12 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="I324">
-        <v>25.19747235387046</v>
+        <v>25.49399457574584</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -15270,21 +15270,21 @@
         <v>2023</v>
       </c>
       <c r="B325">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="I325">
-        <v>24.97262864536678</v>
+        <v>25.35543337070055</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -15316,21 +15316,21 @@
         <v>2023</v>
       </c>
       <c r="B326">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="I326">
-        <v>24.94159801872376</v>
+        <v>25.28644804425129</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -15371,12 +15371,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="I327">
-        <v>24.81324449828387</v>
+        <v>25.19747235387046</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -15408,21 +15408,21 @@
         <v>2023</v>
       </c>
       <c r="B328">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -15441,7 +15441,7 @@
         </is>
       </c>
       <c r="I328">
-        <v>24.7976139752876</v>
+        <v>24.97262864536678</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -15463,12 +15463,12 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="I329">
-        <v>24.74492059267146</v>
+        <v>24.81324449828387</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -15509,12 +15509,12 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="I330">
-        <v>24.72205376996159</v>
+        <v>24.74492059267146</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -15555,12 +15555,12 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="I331">
-        <v>24.68394437420986</v>
+        <v>24.72205376996159</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -15601,12 +15601,12 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -15625,7 +15625,7 @@
         </is>
       </c>
       <c r="I332">
-        <v>24.40724082403243</v>
+        <v>24.68394437420986</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -15647,12 +15647,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="I333">
-        <v>24.15235944608641</v>
+        <v>24.40724082403243</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -15684,21 +15684,21 @@
         <v>2023</v>
       </c>
       <c r="B334">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -15717,7 +15717,7 @@
         </is>
       </c>
       <c r="I334">
-        <v>24.11394000504159</v>
+        <v>24.15235944608641</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -16061,12 +16061,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="I342">
-        <v>22.36070833590424</v>
+        <v>21.77703965123521</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>

--- a/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
@@ -412,21 +412,21 @@
         <v>2023</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Lago Verde</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="I2">
-        <v>37.83783783783784</v>
+        <v>42.40506329113924</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -458,21 +458,21 @@
         <v>2023</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cabo de Hornos</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="I3">
-        <v>35.40885221305327</v>
+        <v>40.63110862887462</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -513,12 +513,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Timaukel</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="I4">
-        <v>34.44444444444444</v>
+        <v>40.18691588785047</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -559,12 +559,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tortel</t>
+          <t>Río Ibáñez</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="I5">
-        <v>33.5243553008596</v>
+        <v>38.1294964028777</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -596,21 +596,21 @@
         <v>2023</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="I6">
-        <v>29.58057395143488</v>
+        <v>34.83483483483483</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -642,21 +642,21 @@
         <v>2023</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="I7">
-        <v>29.57884427032321</v>
+        <v>33.67922971114168</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -688,21 +688,21 @@
         <v>2023</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>San Gregorio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="I8">
-        <v>28.43828414386426</v>
+        <v>32.23684210526316</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -743,12 +743,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="I9">
-        <v>28.03738317757009</v>
+        <v>30.17104846373139</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -780,21 +780,21 @@
         <v>2023</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Timaukel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="I10">
-        <v>27.4368426759189</v>
+        <v>30</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         <v>2023</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="I11">
-        <v>26.11373434613016</v>
+        <v>28.07211184694629</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -872,21 +872,21 @@
         <v>2023</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="I12">
-        <v>26.0217654171705</v>
+        <v>27.59187025251488</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -927,12 +927,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="I13">
-        <v>25.66322256352974</v>
+        <v>26.9900824471263</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -964,21 +964,21 @@
         <v>2023</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="I14">
-        <v>25.00137551581843</v>
+        <v>26.26585709638946</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         <v>2023</v>
       </c>
       <c r="B15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Cisnes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I15">
-        <v>24.26354133671207</v>
+        <v>25.53808948004836</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Gregorio</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I16">
-        <v>23.68421052631579</v>
+        <v>25.47169811320755</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>Guaitecas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="I17">
-        <v>22.9957805907173</v>
+        <v>22.91870714985308</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
+          <t>Tortel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="I18">
-        <v>20.45863309352518</v>
+        <v>20.05730659025788</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         <v>2023</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="I19">
-        <v>19.88795518207283</v>
+        <v>14.32858214553638</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I20">
-        <v>10.36585365853658</v>
+        <v>13.41463414634146</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         <v>2023</v>
       </c>
       <c r="B21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Río Verde</t>
+          <t>O Higgins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="I21">
-        <v>9.433962264150944</v>
+        <v>6.442577030812324</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="I25">
-        <v>53.72091110928378</v>
+        <v>54.45480862013509</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="I26">
-        <v>52.7294438758103</v>
+        <v>53.72091110928378</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1562,21 +1562,21 @@
         <v>2023</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I27">
-        <v>51.52048253329983</v>
+        <v>52.7294438758103</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="I28">
-        <v>51.49797570850202</v>
+        <v>51.52048253329983</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="I29">
-        <v>48.73039581777446</v>
+        <v>51.49797570850202</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         <v>2023</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Ninhue</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="I30">
-        <v>47.34752796824252</v>
+        <v>51.1815734370326</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         <v>2023</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="I31">
-        <v>45.62353365818444</v>
+        <v>49.13762759591693</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         <v>2023</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="I32">
-        <v>45.25951557093425</v>
+        <v>48.97600936220012</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         <v>2023</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I33">
-        <v>44.54673315432809</v>
+        <v>48.73039581777446</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I34">
-        <v>44.32121297206233</v>
+        <v>47.34752796824252</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         <v>2023</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="I35">
-        <v>44.11147011308562</v>
+        <v>46.9206094627105</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="I36">
-        <v>42.94783926123657</v>
+        <v>45.62353365818444</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         <v>2023</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="I37">
-        <v>42.66316926400247</v>
+        <v>45.25951557093425</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         <v>2023</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="I38">
-        <v>42.47900693683826</v>
+        <v>44.54673315432809</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         <v>2023</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="I39">
-        <v>42.42776486217203</v>
+        <v>44.32121297206233</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         <v>2023</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="I40">
-        <v>41.67553757717692</v>
+        <v>44.20996393749165</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         <v>2023</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="I41">
-        <v>41.59894575005491</v>
+        <v>44.11147011308562</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         <v>2023</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I42">
-        <v>41.49421789409617</v>
+        <v>43.15662164886112</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         <v>2023</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="I43">
-        <v>41.35705905357841</v>
+        <v>42.94783926123657</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         <v>2023</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I44">
-        <v>41.09768661609066</v>
+        <v>42.93373815022367</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         <v>2023</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="I45">
-        <v>40.98448727419247</v>
+        <v>42.87163408336407</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I46">
-        <v>40.46981248712137</v>
+        <v>42.66316926400247</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         <v>2023</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="I47">
-        <v>39.99644791759169</v>
+        <v>42.47900693683826</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="I48">
-        <v>39.97377049180328</v>
+        <v>42.42776486217203</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         <v>2023</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="I49">
-        <v>39.93742989260849</v>
+        <v>41.67553757717692</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="I50">
-        <v>39.68501597206745</v>
+        <v>41.59894575005491</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="I51">
-        <v>39.62089077412514</v>
+        <v>41.49421789409617</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         <v>2023</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="I52">
-        <v>39.60848161385728</v>
+        <v>41.35705905357841</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         <v>2023</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="I53">
-        <v>39.35233547231756</v>
+        <v>41.35321100917431</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="I54">
-        <v>39.30318754633061</v>
+        <v>41.09768661609066</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I55">
-        <v>39.23263048738334</v>
+        <v>40.98448727419247</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2896,21 +2896,21 @@
         <v>2023</v>
       </c>
       <c r="B56">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="I56">
-        <v>39.11948725774455</v>
+        <v>40.68332329921734</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         <v>2023</v>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I57">
-        <v>39.0444648478489</v>
+        <v>40.59179556153329</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2988,21 +2988,21 @@
         <v>2023</v>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I58">
-        <v>38.70342451001508</v>
+        <v>40.50619450204711</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         <v>2023</v>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="I59">
-        <v>38.53563902732716</v>
+        <v>40.46981248712137</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         <v>2023</v>
       </c>
       <c r="B60">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="I60">
-        <v>38.45813026140895</v>
+        <v>40.3137730779232</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3126,21 +3126,21 @@
         <v>2023</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="I61">
-        <v>38.16784823161314</v>
+        <v>40.07670182166827</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I62">
-        <v>37.93321871323862</v>
+        <v>39.99644791759169</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         <v>2023</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="I63">
-        <v>37.88838920686835</v>
+        <v>39.97377049180328</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3264,21 +3264,21 @@
         <v>2023</v>
       </c>
       <c r="B64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I64">
-        <v>37.80669514254495</v>
+        <v>39.93742989260849</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         <v>2023</v>
       </c>
       <c r="B65">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="I65">
-        <v>37.68886739997582</v>
+        <v>39.76244991413853</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         <v>2023</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="I66">
-        <v>37.61885468025658</v>
+        <v>39.68501597206745</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         <v>2023</v>
       </c>
       <c r="B67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I67">
-        <v>37.33530093812585</v>
+        <v>39.62089077412514</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         <v>2023</v>
       </c>
       <c r="B68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="I68">
-        <v>37.01768488745981</v>
+        <v>39.60848161385728</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3494,21 +3494,21 @@
         <v>2023</v>
       </c>
       <c r="B69">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I69">
-        <v>36.73091750192752</v>
+        <v>39.57614001666865</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         <v>2023</v>
       </c>
       <c r="B70">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I70">
-        <v>36.68062324112842</v>
+        <v>39.39223410241981</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3586,21 +3586,21 @@
         <v>2023</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="I71">
-        <v>36.48783899480279</v>
+        <v>39.35233547231756</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         <v>2023</v>
       </c>
       <c r="B72">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="I72">
-        <v>36.44416323948118</v>
+        <v>39.30618401206637</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I73">
-        <v>36.27546569507876</v>
+        <v>39.30318754633061</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="I74">
-        <v>35.91801357880038</v>
+        <v>39.23263048738334</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         <v>2023</v>
       </c>
       <c r="B75">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="I75">
-        <v>35.90742504256485</v>
+        <v>39.15553631684077</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         <v>2023</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I76">
-        <v>35.89406651167492</v>
+        <v>39.11948725774455</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         <v>2023</v>
       </c>
       <c r="B77">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="I77">
-        <v>35.79242671109532</v>
+        <v>39.0444648478489</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         <v>2023</v>
       </c>
       <c r="B78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I78">
-        <v>35.74922760041195</v>
+        <v>38.70342451001508</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         <v>2023</v>
       </c>
       <c r="B79">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="I79">
-        <v>35.67816091954023</v>
+        <v>38.61593768723787</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I80">
-        <v>35.66784026390079</v>
+        <v>38.53563902732716</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         <v>2023</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="I81">
-        <v>35.65217391304348</v>
+        <v>38.45813026140895</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         <v>2023</v>
       </c>
       <c r="B82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I82">
-        <v>35.57784302728383</v>
+        <v>38.16784823161314</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="I83">
-        <v>35.47109505280712</v>
+        <v>37.93321871323862</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         <v>2023</v>
       </c>
       <c r="B84">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I84">
-        <v>35.39836646632763</v>
+        <v>37.88838920686835</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="I85">
-        <v>35.26105495422966</v>
+        <v>37.80669514254495</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         <v>2023</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="I86">
-        <v>35.16930990141449</v>
+        <v>37.74034280209267</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4331,12 +4331,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="I87">
-        <v>35.16519463526333</v>
+        <v>37.68886739997582</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         <v>2023</v>
       </c>
       <c r="B88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I88">
-        <v>35.09230605058158</v>
+        <v>37.61885468025658</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4414,21 +4414,21 @@
         <v>2023</v>
       </c>
       <c r="B89">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="I89">
-        <v>35.03923250420915</v>
+        <v>37.43213430757436</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4460,21 +4460,21 @@
         <v>2023</v>
       </c>
       <c r="B90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I90">
-        <v>35.02410061608197</v>
+        <v>37.33530093812585</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         <v>2023</v>
       </c>
       <c r="B91">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="I91">
-        <v>34.97151486031986</v>
+        <v>37.01768488745981</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4552,21 +4552,21 @@
         <v>2023</v>
       </c>
       <c r="B92">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="I92">
-        <v>34.9469918333708</v>
+        <v>36.73091750192752</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         <v>2023</v>
       </c>
       <c r="B93">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I93">
-        <v>34.67736028711638</v>
+        <v>36.69214155175278</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4653,12 +4653,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I94">
-        <v>34.4320404172099</v>
+        <v>36.68062324112842</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         <v>2023</v>
       </c>
       <c r="B95">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I95">
-        <v>34.23672566371682</v>
+        <v>36.56240931629215</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4736,21 +4736,21 @@
         <v>2023</v>
       </c>
       <c r="B96">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I96">
-        <v>34.18774966711052</v>
+        <v>36.48783899480279</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         <v>2023</v>
       </c>
       <c r="B97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="I97">
-        <v>34.16579951439473</v>
+        <v>36.44416323948118</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         <v>2023</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="I98">
-        <v>33.91051179895801</v>
+        <v>36.27546569507876</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="I99">
-        <v>33.90350877192982</v>
+        <v>35.95159487905094</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I100">
-        <v>33.80997177798683</v>
+        <v>35.92972715575323</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         <v>2023</v>
       </c>
       <c r="B101">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I101">
-        <v>33.70034843205575</v>
+        <v>35.91801357880038</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I102">
-        <v>33.58485111303845</v>
+        <v>35.90742504256485</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         <v>2023</v>
       </c>
       <c r="B103">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I103">
-        <v>33.53707414829659</v>
+        <v>35.89406651167492</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         <v>2023</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I104">
-        <v>33.44643372798151</v>
+        <v>35.84498200385034</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="I105">
-        <v>33.3182503770739</v>
+        <v>35.78702788214356</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         <v>2023</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="I106">
-        <v>33.31038890800924</v>
+        <v>35.74922760041195</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="I107">
-        <v>33.24736359468134</v>
+        <v>35.67816091954023</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I108">
-        <v>32.99845336561092</v>
+        <v>35.66784026390079</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5334,21 +5334,21 @@
         <v>2023</v>
       </c>
       <c r="B109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="I109">
-        <v>32.89264939185616</v>
+        <v>35.65217391304348</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5380,21 +5380,21 @@
         <v>2023</v>
       </c>
       <c r="B110">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I110">
-        <v>32.38318737717742</v>
+        <v>35.57784302728383</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         <v>2023</v>
       </c>
       <c r="B111">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="I111">
-        <v>32.06073060978634</v>
+        <v>35.47109505280712</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5481,12 +5481,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="I112">
-        <v>32.0533832826036</v>
+        <v>35.39836646632763</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="I113">
-        <v>31.9653520572216</v>
+        <v>35.28296237149416</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         <v>2023</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="I114">
-        <v>31.94270401573133</v>
+        <v>35.26105495422966</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5610,21 +5610,21 @@
         <v>2023</v>
       </c>
       <c r="B115">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Ránquil</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="I115">
-        <v>31.81333849953988</v>
+        <v>35.23230088495576</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5656,21 +5656,21 @@
         <v>2023</v>
       </c>
       <c r="B116">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="I116">
-        <v>31.0788476849953</v>
+        <v>35.16930990141449</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -5702,21 +5702,21 @@
         <v>2023</v>
       </c>
       <c r="B117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I117">
-        <v>30.98179039857379</v>
+        <v>35.16519463526333</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         <v>2023</v>
       </c>
       <c r="B118">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="I118">
-        <v>30.96540550843419</v>
+        <v>35.09230605058158</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5794,21 +5794,21 @@
         <v>2023</v>
       </c>
       <c r="B119">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="I119">
-        <v>30.84421500151837</v>
+        <v>35.03923250420915</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         <v>2023</v>
       </c>
       <c r="B120">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I120">
-        <v>30.66593404336172</v>
+        <v>35.02410061608197</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="I121">
-        <v>30.6238260800064</v>
+        <v>34.97899920341806</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -5932,21 +5932,21 @@
         <v>2023</v>
       </c>
       <c r="B122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I122">
-        <v>30.54745375762941</v>
+        <v>34.97151486031986</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -5987,12 +5987,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I123">
-        <v>30.51222762188431</v>
+        <v>34.70454941607112</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6024,21 +6024,21 @@
         <v>2023</v>
       </c>
       <c r="B124">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I124">
-        <v>30.47210300429185</v>
+        <v>34.67736028711638</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6070,21 +6070,21 @@
         <v>2023</v>
       </c>
       <c r="B125">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="I125">
-        <v>30.44702569517775</v>
+        <v>34.63327257871913</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         <v>2023</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="I126">
-        <v>30.40264423076923</v>
+        <v>34.4320404172099</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         <v>2023</v>
       </c>
       <c r="B127">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I127">
-        <v>30.19117198703689</v>
+        <v>34.16579951439473</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         <v>2023</v>
       </c>
       <c r="B128">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="I128">
-        <v>30.15543375867089</v>
+        <v>33.91051179895801</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6263,12 +6263,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="I129">
-        <v>29.87188426006624</v>
+        <v>33.74369098985782</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         <v>2023</v>
       </c>
       <c r="B130">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="I130">
-        <v>29.33844678811122</v>
+        <v>33.70034843205575</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6346,21 +6346,21 @@
         <v>2023</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="I131">
-        <v>29.14199793252514</v>
+        <v>33.61158983196898</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         <v>2023</v>
       </c>
       <c r="B132">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I132">
-        <v>29.00376726663876</v>
+        <v>33.58485111303845</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         <v>2023</v>
       </c>
       <c r="B133">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="I133">
-        <v>28.96435776731674</v>
+        <v>33.53707414829659</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         <v>2023</v>
       </c>
       <c r="B134">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="I134">
-        <v>28.76666337513577</v>
+        <v>33.50946365906736</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6530,21 +6530,21 @@
         <v>2023</v>
       </c>
       <c r="B135">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I135">
-        <v>28.67298578199052</v>
+        <v>33.44643372798151</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="I136">
-        <v>28.58309817317689</v>
+        <v>33.34362886661622</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         <v>2023</v>
       </c>
       <c r="B137">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="I137">
-        <v>28.54175742900275</v>
+        <v>33.31038890800924</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         <v>2023</v>
       </c>
       <c r="B138">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="I138">
-        <v>28.4129323047586</v>
+        <v>33.24736359468134</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6714,21 +6714,21 @@
         <v>2023</v>
       </c>
       <c r="B139">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="I139">
-        <v>28.2897550782866</v>
+        <v>32.99845336561092</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         <v>2023</v>
       </c>
       <c r="B140">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="I140">
-        <v>28.22055873575028</v>
+        <v>32.89264939185616</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I141">
-        <v>28.1533688282836</v>
+        <v>32.7849848911118</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -6852,21 +6852,21 @@
         <v>2023</v>
       </c>
       <c r="B142">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I142">
-        <v>28.08205271817132</v>
+        <v>32.38318737717742</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -6907,12 +6907,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I143">
-        <v>27.94965593388577</v>
+        <v>32.35646315712496</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -6944,21 +6944,21 @@
         <v>2023</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I144">
-        <v>27.83568362967505</v>
+        <v>32.23839474248805</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -6990,21 +6990,21 @@
         <v>2023</v>
       </c>
       <c r="B145">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="I145">
-        <v>27.74338773213281</v>
+        <v>32.0533832826036</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I146">
-        <v>27.584875667083</v>
+        <v>31.99727489496991</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         <v>2023</v>
       </c>
       <c r="B147">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="I147">
-        <v>27.55531749843005</v>
+        <v>31.94270401573133</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7128,21 +7128,21 @@
         <v>2023</v>
       </c>
       <c r="B148">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I148">
-        <v>27.4742995363838</v>
+        <v>31.81333849953988</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7174,21 +7174,21 @@
         <v>2023</v>
       </c>
       <c r="B149">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="I149">
-        <v>27.39553520320549</v>
+        <v>31.6598122858973</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         <v>2023</v>
       </c>
       <c r="B150">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I150">
-        <v>27.28896297178235</v>
+        <v>31.0788476849953</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         <v>2023</v>
       </c>
       <c r="B151">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I151">
-        <v>27.17278706164829</v>
+        <v>30.98179039857379</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7321,12 +7321,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I152">
-        <v>27.09688716477418</v>
+        <v>30.93531823722803</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7358,21 +7358,21 @@
         <v>2023</v>
       </c>
       <c r="B153">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I153">
-        <v>27.08032178995663</v>
+        <v>30.84421500151837</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="I154">
-        <v>27.06691464736342</v>
+        <v>30.67702396201803</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="I155">
-        <v>27.05221168908771</v>
+        <v>30.63029162746943</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -7496,21 +7496,21 @@
         <v>2023</v>
       </c>
       <c r="B156">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="I156">
-        <v>26.8659379879545</v>
+        <v>30.54745375762941</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         <v>2023</v>
       </c>
       <c r="B157">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="I157">
-        <v>26.7682437850842</v>
+        <v>30.40264423076923</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -7588,21 +7588,21 @@
         <v>2023</v>
       </c>
       <c r="B158">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="I158">
-        <v>26.7152342309111</v>
+        <v>30.33609079646725</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I159">
-        <v>26.30363744180472</v>
+        <v>30.31104966920115</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -7680,21 +7680,21 @@
         <v>2023</v>
       </c>
       <c r="B160">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I160">
-        <v>26.24412476855149</v>
+        <v>30.06651693158258</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         <v>2023</v>
       </c>
       <c r="B161">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="I161">
-        <v>26.13864030987044</v>
+        <v>29.65352694434111</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -7772,21 +7772,21 @@
         <v>2023</v>
       </c>
       <c r="B162">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="I162">
-        <v>25.88376273217495</v>
+        <v>29.46336231662006</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -7818,21 +7818,21 @@
         <v>2023</v>
       </c>
       <c r="B163">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I163">
-        <v>25.82824059183017</v>
+        <v>29.28299220690246</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="I164">
-        <v>25.80925483380404</v>
+        <v>29.18114062984165</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="I165">
-        <v>25.76076286635816</v>
+        <v>29.14199793252514</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="I166">
-        <v>25.75039758935297</v>
+        <v>29.14098599746173</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I167">
-        <v>25.72203087720602</v>
+        <v>29.07749015759008</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8057,12 +8057,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="I168">
-        <v>25.6521016780196</v>
+        <v>29.06803574227935</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8094,21 +8094,21 @@
         <v>2023</v>
       </c>
       <c r="B169">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I169">
-        <v>25.59936888284567</v>
+        <v>29.00376726663876</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -8140,21 +8140,21 @@
         <v>2023</v>
       </c>
       <c r="B170">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>La Pintana</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="I170">
-        <v>25.59935503033903</v>
+        <v>28.95599333876626</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -8195,12 +8195,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I171">
-        <v>25.20578916362826</v>
+        <v>28.31639082584222</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8232,21 +8232,21 @@
         <v>2023</v>
       </c>
       <c r="B172">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="I172">
-        <v>25.17171780388966</v>
+        <v>27.83568362967505</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8287,12 +8287,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I173">
-        <v>25.08145580589255</v>
+        <v>27.21250526359033</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -8324,21 +8324,21 @@
         <v>2023</v>
       </c>
       <c r="B174">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="I174">
-        <v>25.05733944954128</v>
+        <v>26.8659379879545</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="I175">
-        <v>24.83400514730942</v>
+        <v>26.58454141023929</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         <v>2023</v>
       </c>
       <c r="B176">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="I176">
-        <v>24.76178709866724</v>
+        <v>26.57953918615013</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -8462,21 +8462,21 @@
         <v>2023</v>
       </c>
       <c r="B177">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="I177">
-        <v>24.75319473245777</v>
+        <v>26.24412476855149</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -8517,12 +8517,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I178">
-        <v>24.70674666340149</v>
+        <v>25.96707105719237</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -8554,21 +8554,21 @@
         <v>2023</v>
       </c>
       <c r="B179">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="I179">
-        <v>24.55055726225531</v>
+        <v>25.76076286635816</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         <v>2023</v>
       </c>
       <c r="B180">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I180">
-        <v>24.31947352677236</v>
+        <v>25.48591748494767</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -8646,21 +8646,21 @@
         <v>2023</v>
       </c>
       <c r="B181">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="I181">
-        <v>24.0784084259801</v>
+        <v>25.2562008020199</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -8701,12 +8701,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="I182">
-        <v>24.05930162552679</v>
+        <v>25.05816089139219</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -8747,12 +8747,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="I183">
-        <v>23.6739806496199</v>
+        <v>24.19318852943107</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -8784,21 +8784,21 @@
         <v>2023</v>
       </c>
       <c r="B184">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="I184">
-        <v>23.64508738223176</v>
+        <v>23.66844207723036</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="I185">
-        <v>22.50593237097093</v>
+        <v>23.440388830649</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="I188">
-        <v>20.6620319907376</v>
+        <v>20.56498757307383</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9023,12 +9023,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="I189">
-        <v>20.47803074855079</v>
+        <v>19.59973652948165</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -9069,12 +9069,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I190">
-        <v>19.36217046993852</v>
+        <v>18.90687045778078</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -9115,12 +9115,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="I191">
-        <v>17.57577717921876</v>
+        <v>17.79239766081871</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9161,12 +9161,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="I192">
-        <v>14.95287804967229</v>
+        <v>17.30144923985348</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -9198,21 +9198,21 @@
         <v>2023</v>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="I193">
-        <v>49.47596073864581</v>
+        <v>56.04719764011799</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -9253,12 +9253,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="I194">
-        <v>49.41060903732809</v>
+        <v>49.47596073864581</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9299,12 +9299,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="I195">
-        <v>44.92035024791645</v>
+        <v>49.41060903732809</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -9336,21 +9336,21 @@
         <v>2023</v>
       </c>
       <c r="B196">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Alto del Carmen</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="I196">
-        <v>44.03973509933775</v>
+        <v>44.92035024791645</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -9382,21 +9382,21 @@
         <v>2023</v>
       </c>
       <c r="B197">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Camiña</t>
+          <t>Alto del Carmen</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="I197">
-        <v>40.63860667634253</v>
+        <v>44.03973509933775</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="I198">
-        <v>39.21568627450981</v>
+        <v>42.64705882352941</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -9474,21 +9474,21 @@
         <v>2023</v>
       </c>
       <c r="B199">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="I199">
-        <v>38.17379182156134</v>
+        <v>40.63860667634253</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -9520,21 +9520,21 @@
         <v>2023</v>
       </c>
       <c r="B200">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="I200">
-        <v>37.79017961825259</v>
+        <v>38.54166666666667</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -9575,12 +9575,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="I201">
-        <v>37.38823825714645</v>
+        <v>38.17379182156134</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="I202">
-        <v>36.59891427850019</v>
+        <v>37.79017961825259</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="I203">
-        <v>36.29968343299332</v>
+        <v>37.38823825714645</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -9704,21 +9704,21 @@
         <v>2023</v>
       </c>
       <c r="B204">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Huasco</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="I204">
-        <v>36.06220280169644</v>
+        <v>36.59891427850019</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         <v>2023</v>
       </c>
       <c r="B205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I205">
-        <v>36.05778745299822</v>
+        <v>36.29968343299332</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         <v>2023</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Huasco</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="I206">
-        <v>35.71065989847716</v>
+        <v>36.06220280169644</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -9842,21 +9842,21 @@
         <v>2023</v>
       </c>
       <c r="B207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Freirina</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="I207">
-        <v>35.52851935769875</v>
+        <v>36.05778745299822</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -9888,21 +9888,21 @@
         <v>2023</v>
       </c>
       <c r="B208">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="I208">
-        <v>34.50520833333333</v>
+        <v>35.71065989847716</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -9943,12 +9943,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="I209">
-        <v>34.35695799323113</v>
+        <v>35.52851935769875</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I210">
-        <v>34.34106098579782</v>
+        <v>34.35695799323113</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10026,21 +10026,21 @@
         <v>2023</v>
       </c>
       <c r="B211">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I211">
-        <v>33.92330383480826</v>
+        <v>34.34106098579782</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -10394,21 +10394,21 @@
         <v>2023</v>
       </c>
       <c r="B219">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="I219">
-        <v>30.77715557016268</v>
+        <v>30.13004683143719</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -10449,12 +10449,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="I220">
-        <v>30.13004683143719</v>
+        <v>29.98318474570894</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -10486,21 +10486,21 @@
         <v>2023</v>
       </c>
       <c r="B221">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I221">
-        <v>29.98318474570894</v>
+        <v>29.27416602409334</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -11222,21 +11222,21 @@
         <v>2023</v>
       </c>
       <c r="B237">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I237">
-        <v>46.77833310819938</v>
+        <v>47.58732081566727</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -11277,12 +11277,12 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="I238">
-        <v>45.2066467831274</v>
+        <v>46.77833310819938</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -11314,21 +11314,21 @@
         <v>2023</v>
       </c>
       <c r="B239">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="I239">
-        <v>45.14980096375445</v>
+        <v>46.76481983727238</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -11360,21 +11360,21 @@
         <v>2023</v>
       </c>
       <c r="B240">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="I240">
-        <v>44.86350574712644</v>
+        <v>46.70411555657457</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -11406,21 +11406,21 @@
         <v>2023</v>
       </c>
       <c r="B241">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="I241">
-        <v>42.56713554987212</v>
+        <v>46.2852835245833</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -11452,21 +11452,21 @@
         <v>2023</v>
       </c>
       <c r="B242">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="I242">
-        <v>40.51179793951479</v>
+        <v>45.76425164660458</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -11507,12 +11507,12 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="I243">
-        <v>40.43387349712494</v>
+        <v>45.2066467831274</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -11553,12 +11553,12 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="I244">
-        <v>39.61114437673911</v>
+        <v>45.14980096375445</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -11590,21 +11590,21 @@
         <v>2023</v>
       </c>
       <c r="B245">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="I245">
-        <v>39.1516975453776</v>
+        <v>45.01832722425858</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -11636,21 +11636,21 @@
         <v>2023</v>
       </c>
       <c r="B246">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I246">
-        <v>37.85622357050929</v>
+        <v>44.86350574712644</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -11682,21 +11682,21 @@
         <v>2023</v>
       </c>
       <c r="B247">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="I247">
-        <v>37.82996712071395</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -11728,21 +11728,21 @@
         <v>2023</v>
       </c>
       <c r="B248">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="I248">
-        <v>37.25377334356612</v>
+        <v>44.07803525450584</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -11774,21 +11774,21 @@
         <v>2023</v>
       </c>
       <c r="B249">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="I249">
-        <v>36.8324421825678</v>
+        <v>43.68434113657044</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -11820,21 +11820,21 @@
         <v>2023</v>
       </c>
       <c r="B250">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="I250">
-        <v>36.69429097605893</v>
+        <v>43.31273176761434</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -11866,21 +11866,21 @@
         <v>2023</v>
       </c>
       <c r="B251">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="I251">
-        <v>36.52335675899132</v>
+        <v>43.11704063068527</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -11921,12 +11921,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I252">
-        <v>35.83060247038064</v>
+        <v>42.56713554987212</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -11958,21 +11958,21 @@
         <v>2023</v>
       </c>
       <c r="B253">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="I253">
-        <v>35.75220352564102</v>
+        <v>42.44992295839754</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -12004,21 +12004,21 @@
         <v>2023</v>
       </c>
       <c r="B254">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="I254">
-        <v>35.43320878094349</v>
+        <v>41.96196038197459</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -12050,21 +12050,21 @@
         <v>2023</v>
       </c>
       <c r="B255">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="I255">
-        <v>35.04997101856569</v>
+        <v>41.6316958775611</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -12096,21 +12096,21 @@
         <v>2023</v>
       </c>
       <c r="B256">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="I256">
-        <v>34.5697851860547</v>
+        <v>41.02717229023589</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -12142,21 +12142,21 @@
         <v>2023</v>
       </c>
       <c r="B257">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="I257">
-        <v>34.38579181055748</v>
+        <v>40.72064250054265</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -12197,12 +12197,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="I258">
-        <v>34.18961628377313</v>
+        <v>40.51179793951479</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -12234,21 +12234,21 @@
         <v>2023</v>
       </c>
       <c r="B259">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -12267,7 +12267,7 @@
         </is>
       </c>
       <c r="I259">
-        <v>33.9924670433145</v>
+        <v>40.49422575437725</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -12289,12 +12289,12 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="I260">
-        <v>33.51747058295159</v>
+        <v>40.43387349712494</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -12326,21 +12326,21 @@
         <v>2023</v>
       </c>
       <c r="B261">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="I261">
-        <v>33.376611747851</v>
+        <v>40.20125473631902</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -12372,21 +12372,21 @@
         <v>2023</v>
       </c>
       <c r="B262">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="I262">
-        <v>33.18507890961263</v>
+        <v>39.93846153846154</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -12427,12 +12427,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I263">
-        <v>32.88755458515284</v>
+        <v>39.66754364984453</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -12473,12 +12473,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="I264">
-        <v>32.8234658988663</v>
+        <v>39.6375485426059</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -12510,21 +12510,21 @@
         <v>2023</v>
       </c>
       <c r="B265">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="I265">
-        <v>32.71940667490729</v>
+        <v>39.61114437673911</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -12556,21 +12556,21 @@
         <v>2023</v>
       </c>
       <c r="B266">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="I266">
-        <v>32.00025554206862</v>
+        <v>39.52493177871496</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         <v>2023</v>
       </c>
       <c r="B267">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="I267">
-        <v>31.88567404190387</v>
+        <v>39.36580660718592</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -12648,21 +12648,21 @@
         <v>2023</v>
       </c>
       <c r="B268">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="I268">
-        <v>31.57215772056761</v>
+        <v>39.23758182518291</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         <v>2023</v>
       </c>
       <c r="B269">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="I269">
-        <v>31.41010101010101</v>
+        <v>39.17631623980377</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -12740,21 +12740,21 @@
         <v>2023</v>
       </c>
       <c r="B270">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="I270">
-        <v>31.33427082471669</v>
+        <v>39.1516975453776</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -12795,12 +12795,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="I271">
-        <v>31.16888744448055</v>
+        <v>38.99330997132845</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="I272">
-        <v>31.16040032458751</v>
+        <v>38.76798876798877</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -12887,12 +12887,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="I273">
-        <v>31.06972518737224</v>
+        <v>38.5583721331264</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -12924,21 +12924,21 @@
         <v>2023</v>
       </c>
       <c r="B274">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="I274">
-        <v>31.02894477497536</v>
+        <v>38.21579264617239</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -12970,21 +12970,21 @@
         <v>2023</v>
       </c>
       <c r="B275">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="I275">
-        <v>31.00607279619387</v>
+        <v>37.85946196660483</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -13016,21 +13016,21 @@
         <v>2023</v>
       </c>
       <c r="B276">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="I276">
-        <v>30.93306288032454</v>
+        <v>37.84365802885651</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         <v>2023</v>
       </c>
       <c r="B277">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -13095,7 +13095,7 @@
         </is>
       </c>
       <c r="I277">
-        <v>30.73514784338548</v>
+        <v>37.82996712071395</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -13108,21 +13108,21 @@
         <v>2023</v>
       </c>
       <c r="B278">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Lago Ranco</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="I278">
-        <v>30.52075201249088</v>
+        <v>37.79210314262691</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -13154,21 +13154,21 @@
         <v>2023</v>
       </c>
       <c r="B279">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="I279">
-        <v>30.33754920847642</v>
+        <v>37.53044781712573</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -13200,21 +13200,21 @@
         <v>2023</v>
       </c>
       <c r="B280">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -13233,7 +13233,7 @@
         </is>
       </c>
       <c r="I280">
-        <v>30.29890921390118</v>
+        <v>37.4248496993988</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -13246,21 +13246,21 @@
         <v>2023</v>
       </c>
       <c r="B281">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="I281">
-        <v>30.22203947368421</v>
+        <v>37.25377334356612</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -13292,21 +13292,21 @@
         <v>2023</v>
       </c>
       <c r="B282">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="I282">
-        <v>30.21960013110456</v>
+        <v>36.9814302647175</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -13338,21 +13338,21 @@
         <v>2023</v>
       </c>
       <c r="B283">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="I283">
-        <v>30.1460883811951</v>
+        <v>36.83419602604776</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -13384,21 +13384,21 @@
         <v>2023</v>
       </c>
       <c r="B284">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="I284">
-        <v>29.64576407199358</v>
+        <v>36.8324421825678</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -13430,21 +13430,21 @@
         <v>2023</v>
       </c>
       <c r="B285">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -13463,7 +13463,7 @@
         </is>
       </c>
       <c r="I285">
-        <v>29.63632710468154</v>
+        <v>36.69429097605893</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -13476,21 +13476,21 @@
         <v>2023</v>
       </c>
       <c r="B286">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="I286">
-        <v>29.57406449387825</v>
+        <v>36.52335675899132</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -13522,21 +13522,21 @@
         <v>2023</v>
       </c>
       <c r="B287">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="I287">
-        <v>29.52029520295203</v>
+        <v>36.06592465753425</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I288">
-        <v>29.47914154810706</v>
+        <v>36.06085526315789</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -13614,21 +13614,21 @@
         <v>2023</v>
       </c>
       <c r="B289">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Hualpén</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -13647,7 +13647,7 @@
         </is>
       </c>
       <c r="I289">
-        <v>29.47588126159555</v>
+        <v>35.83060247038064</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -13660,21 +13660,21 @@
         <v>2023</v>
       </c>
       <c r="B290">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -13693,7 +13693,7 @@
         </is>
       </c>
       <c r="I290">
-        <v>29.18372075063711</v>
+        <v>35.75220352564102</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -13706,21 +13706,21 @@
         <v>2023</v>
       </c>
       <c r="B291">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="I291">
-        <v>29.13669064748202</v>
+        <v>35.71227477477478</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -13761,12 +13761,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="I292">
-        <v>29.13448207565855</v>
+        <v>35.43806898855759</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -13798,21 +13798,21 @@
         <v>2023</v>
       </c>
       <c r="B293">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="I293">
-        <v>29.11217247690042</v>
+        <v>35.43320878094349</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -13844,21 +13844,21 @@
         <v>2023</v>
       </c>
       <c r="B294">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="I294">
-        <v>29.0653115628124</v>
+        <v>35.04997101856569</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -13890,21 +13890,21 @@
         <v>2023</v>
       </c>
       <c r="B295">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="I295">
-        <v>29.0115211220571</v>
+        <v>34.91183209909342</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         <v>2023</v>
       </c>
       <c r="B296">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="I296">
-        <v>28.96959459459459</v>
+        <v>34.88678251711427</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -13991,12 +13991,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -14015,7 +14015,7 @@
         </is>
       </c>
       <c r="I297">
-        <v>28.91705544775195</v>
+        <v>34.67521834061135</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -14037,12 +14037,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -14061,7 +14061,7 @@
         </is>
       </c>
       <c r="I298">
-        <v>28.85380996130182</v>
+        <v>34.53302141443225</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -14074,21 +14074,21 @@
         <v>2023</v>
       </c>
       <c r="B299">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="I299">
-        <v>28.80741337630943</v>
+        <v>34.38579181055748</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="I300">
-        <v>28.78201240845267</v>
+        <v>34.20599008834303</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -14166,21 +14166,21 @@
         <v>2023</v>
       </c>
       <c r="B301">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I301">
-        <v>28.77197341449779</v>
+        <v>34.18961628377313</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -14221,12 +14221,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="I302">
-        <v>28.60646854144088</v>
+        <v>34.16902071563089</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -14258,21 +14258,21 @@
         <v>2023</v>
       </c>
       <c r="B303">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -14291,7 +14291,7 @@
         </is>
       </c>
       <c r="I303">
-        <v>28.4611522530438</v>
+        <v>34.16565164433617</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -14313,12 +14313,12 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Futrono</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="I304">
-        <v>28.34685234369392</v>
+        <v>34.08083913554571</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -14359,12 +14359,12 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -14383,7 +14383,7 @@
         </is>
       </c>
       <c r="I305">
-        <v>28.30508474576271</v>
+        <v>34.03293135435992</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -14396,21 +14396,21 @@
         <v>2023</v>
       </c>
       <c r="B306">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="I306">
-        <v>28.27265074187099</v>
+        <v>33.80183797976678</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -14442,21 +14442,21 @@
         <v>2023</v>
       </c>
       <c r="B307">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="I307">
-        <v>28.15997987674506</v>
+        <v>33.58848489891006</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -14488,21 +14488,21 @@
         <v>2023</v>
       </c>
       <c r="B308">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="I308">
-        <v>27.97124971017853</v>
+        <v>33.51747058295159</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -14534,21 +14534,21 @@
         <v>2023</v>
       </c>
       <c r="B309">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="I309">
-        <v>27.95733678086619</v>
+        <v>33.43868520859672</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -14589,12 +14589,12 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="I310">
-        <v>27.86802889734671</v>
+        <v>33.41784989858012</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -14626,21 +14626,21 @@
         <v>2023</v>
       </c>
       <c r="B311">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="I311">
-        <v>27.77221108884436</v>
+        <v>33.376611747851</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -14672,21 +14672,21 @@
         <v>2023</v>
       </c>
       <c r="B312">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="I312">
-        <v>27.74505494505495</v>
+        <v>33.18507890961263</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -14718,21 +14718,21 @@
         <v>2023</v>
       </c>
       <c r="B313">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -14751,7 +14751,7 @@
         </is>
       </c>
       <c r="I313">
-        <v>27.67084106369821</v>
+        <v>33.05754734326163</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -14773,12 +14773,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="I314">
-        <v>27.40115223739247</v>
+        <v>32.88522806744891</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -14810,21 +14810,21 @@
         <v>2023</v>
       </c>
       <c r="B315">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="I315">
-        <v>27.3234046093685</v>
+        <v>32.85234535803271</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -14856,21 +14856,21 @@
         <v>2023</v>
       </c>
       <c r="B316">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -14889,7 +14889,7 @@
         </is>
       </c>
       <c r="I316">
-        <v>27.19068676112264</v>
+        <v>32.54773216605278</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -14911,12 +14911,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="I317">
-        <v>27.05787105513086</v>
+        <v>32.42359451641303</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -14948,21 +14948,21 @@
         <v>2023</v>
       </c>
       <c r="B318">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="I318">
-        <v>26.80860983759422</v>
+        <v>31.94275857663068</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="I319">
-        <v>26.37560637560637</v>
+        <v>31.88567404190387</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -15049,12 +15049,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="I320">
-        <v>26.2898049864231</v>
+        <v>31.75946231499321</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="I321">
-        <v>26.10619469026549</v>
+        <v>31.58740008030076</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -15132,21 +15132,21 @@
         <v>2023</v>
       </c>
       <c r="B322">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="I322">
-        <v>25.73802949454413</v>
+        <v>31.57215772056761</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -15178,21 +15178,21 @@
         <v>2023</v>
       </c>
       <c r="B323">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="I323">
-        <v>25.51739719837325</v>
+        <v>31.45793886935353</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -15224,21 +15224,21 @@
         <v>2023</v>
       </c>
       <c r="B324">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="I324">
-        <v>25.49399457574584</v>
+        <v>31.41010101010101</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -15270,21 +15270,21 @@
         <v>2023</v>
       </c>
       <c r="B325">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="I325">
-        <v>25.35543337070055</v>
+        <v>30.72258245090265</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -15316,21 +15316,21 @@
         <v>2023</v>
       </c>
       <c r="B326">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="I326">
-        <v>25.28644804425129</v>
+        <v>30.52075201249088</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -15362,21 +15362,21 @@
         <v>2023</v>
       </c>
       <c r="B327">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Los Ángeles</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="I327">
-        <v>25.19747235387046</v>
+        <v>30.29890921390118</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -15408,21 +15408,21 @@
         <v>2023</v>
       </c>
       <c r="B328">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -15441,7 +15441,7 @@
         </is>
       </c>
       <c r="I328">
-        <v>24.97262864536678</v>
+        <v>30.24127211488061</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -15454,21 +15454,21 @@
         <v>2023</v>
       </c>
       <c r="B329">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="I329">
-        <v>24.81324449828387</v>
+        <v>29.33121881406413</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="I330">
-        <v>24.74492059267146</v>
+        <v>29.11010558069382</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -15546,21 +15546,21 @@
         <v>2023</v>
       </c>
       <c r="B331">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="I331">
-        <v>24.72205376996159</v>
+        <v>28.48767598365055</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -15592,21 +15592,21 @@
         <v>2023</v>
       </c>
       <c r="B332">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Los Álamos</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -15625,7 +15625,7 @@
         </is>
       </c>
       <c r="I332">
-        <v>24.68394437420986</v>
+        <v>28.4611522530438</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -15647,12 +15647,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -15671,7 +15671,7 @@
         </is>
       </c>
       <c r="I333">
-        <v>24.40724082403243</v>
+        <v>28.21247233433147</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -15693,12 +15693,12 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -15717,7 +15717,7 @@
         </is>
       </c>
       <c r="I334">
-        <v>24.15235944608641</v>
+        <v>27.41629816803538</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -15739,12 +15739,12 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="I335">
-        <v>23.92979452054794</v>
+        <v>26.55214142902241</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -15776,21 +15776,21 @@
         <v>2023</v>
       </c>
       <c r="B336">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="I336">
-        <v>23.83804192162479</v>
+        <v>26.37560637560637</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -15831,12 +15831,12 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -15855,7 +15855,7 @@
         </is>
       </c>
       <c r="I337">
-        <v>23.79237551223147</v>
+        <v>26.02032317174746</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -15868,21 +15868,21 @@
         <v>2023</v>
       </c>
       <c r="B338">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -15901,7 +15901,7 @@
         </is>
       </c>
       <c r="I338">
-        <v>23.20341047503045</v>
+        <v>25.51739719837325</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
@@ -15923,12 +15923,12 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="I339">
-        <v>23.18059299191374</v>
+        <v>23.67867810474469</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -15960,21 +15960,21 @@
         <v>2023</v>
       </c>
       <c r="B340">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -15993,7 +15993,7 @@
         </is>
       </c>
       <c r="I340">
-        <v>23.07827307827308</v>
+        <v>22.12701021246625</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -16006,21 +16006,21 @@
         <v>2023</v>
       </c>
       <c r="B341">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -16039,7 +16039,7 @@
         </is>
       </c>
       <c r="I341">
-        <v>22.46580475922803</v>
+        <v>21.77703965123521</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -16052,21 +16052,21 @@
         <v>2023</v>
       </c>
       <c r="B342">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="I342">
-        <v>21.77703965123521</v>
+        <v>21.21029445861349</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>

--- a/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:07</t>
+    <t xml:space="preserve">2026-09-07 12:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2179,16 +2179,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_d_depmayores_a_2023.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Otras relaciones demográficas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13577,23 +13586,23 @@
         <v>721</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -13615,21 +13624,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13638,7 +13647,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmayores_a_2023.xlsx
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:46</t>
+    <t xml:space="preserve">2026-09-08 10:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
